--- a/satisfaction_surveys/004_volunteer_satisfaction_survey--satisfaction_surveys.xlsx
+++ b/satisfaction_surveys/004_volunteer_satisfaction_survey--satisfaction_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,43 +525,43 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>volunteer_satisfaction</t>
+          <t>How would you rate the overall project satisfaction?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>project_name</t>
+          <t>project_satisfaction</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>project_name</t>
+          <t>How satisfied are you with project communication?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -571,36 +571,36 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>volunteering_experience</t>
+          <t>How satisfied are you with your role/position within the project?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>project_communication_issues</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>Have you had any issues with project communication?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,18 +612,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>improve_project_communication</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>What do you think is the most valuable thing that we could do to improve project communication?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,41 +635,41 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>volunteer_satisfaction</t>
+          <t>volunteer_satisfaction_improvement</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>volunteer_satisfaction</t>
+          <t>What do you think is the most valuable thing that we could do to improve your role/position within the project?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>project_satisfaction</t>
+          <t>overall_satisfaction</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>project_satisfaction</t>
+          <t>How satisfied are you with the overall project process?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,64 +681,110 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>communication_satisfaction</t>
+          <t>project_efficiency</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>communication_satisfaction</t>
+          <t>What do you think we could do to make the project more efficient?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>project_satisfaction</t>
+          <t>project_comments</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>project_satisfaction</t>
+          <t>What do you like or dislike about the project?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>communication_satisfaction</t>
+          <t>participation_goal</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>communication_satisfaction</t>
+          <t>What is the main reason for your participation in this project?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>involvement_alignment</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Do you think your involvement in this project aligns with your personal goals?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>future_participation</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>How likely are you to participate in future projects like this?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -753,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="39" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -803,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -820,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -837,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Option 4</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -854,97 +900,386 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_5</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Option 5</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>communication_satisfaction_choices</t>
+          <t>volunteer_experience_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>communication_satisfaction_choices</t>
+          <t>volunteer_experience_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>communication_satisfaction_choices</t>
+          <t>volunteer_experience_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>communication_satisfaction_choices</t>
+          <t>volunteer_experience_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Option 4</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>communication_satisfaction_choices</t>
+          <t>volunteer_experience_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option_5</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Option 5</t>
+          <t>Very Dissatisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>project_communication_issues_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>no_issues</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>No issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>project_communication_issues_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>difficulty_understanding_instructions</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Difficulty understanding instructions</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>project_communication_issues_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>unresponsive_team_members</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Unresponsive team members</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>project_communication_issues_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>overall_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>very_satisfied</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Very Satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>overall_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>somewhat_satisfied</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Somewhat Satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>overall_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>overall_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>somewhat_dissatisfied</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Somewhat Dissatisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>overall_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>very_dissatisfied</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Very Dissatisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>involvement_alignment_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>involvement_alignment_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>involvement_alignment_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>undecided</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Undecided</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>future_participation_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>very_likely</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Very Likely</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>future_participation_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>somewhat_likely</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Somewhat Likely</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>future_participation_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>undecided</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Undecided</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>future_participation_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>not_likely</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Not Likely</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>future_participation_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>very_unlikely</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Very Unlikely</t>
         </is>
       </c>
     </row>
